--- a/IDI_Team.xlsx
+++ b/IDI_Team.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://socotecgroup.sharepoint.com/sites/SOCOTECLIBAN/KSA Shared Documents/List of Employees/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\rd6_generator_tool\rd6_deploy\rd6_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="761" documentId="8_{B844E202-FB08-45DD-BD39-93EE14C7AAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F636EDF-E486-4A82-AB2F-1FE780D3E296}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D1D883-A426-4227-935D-A0FD8E808670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="5" activeTab="3" xr2:uid="{5ABAA1C1-B119-44A8-8322-349E275CC8CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5ABAA1C1-B119-44A8-8322-349E275CC8CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Current Staff" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="2760" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="357">
   <si>
     <t>KSA STAFF</t>
   </si>
@@ -1114,6 +1114,12 @@
   </si>
   <si>
     <t>25 (including HR, Accounting, Quality, IT &amp; office boy)</t>
+  </si>
+  <si>
+    <t>Ali KAMAL</t>
+  </si>
+  <si>
+    <t>ali.kamal@socotec.com</t>
   </si>
 </sst>
 </file>
@@ -1121,10 +1127,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1369,7 +1375,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1624,13 +1630,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1669,10 +1695,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1779,7 +1805,7 @@
     <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1839,6 +1865,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1854,9 +1883,8 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -1885,7 +1913,7 @@
     <cacheField name="Emp. ID" numFmtId="0">
       <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="20055" maxValue="34294"/>
     </cacheField>
-    <cacheField name="Joining Date" numFmtId="164">
+    <cacheField name="Joining Date" numFmtId="165">
       <sharedItems containsDate="1" containsBlank="1" containsMixedTypes="1" minDate="2022-07-15T00:00:00" maxDate="2025-10-06T00:00:00"/>
     </cacheField>
     <cacheField name="Name" numFmtId="0">
@@ -2744,7 +2772,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7165A24-A7E6-4B06-A81F-C5410B69138D}" name="Tableau croisé dynamique1" cacheId="2760" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7165A24-A7E6-4B06-A81F-C5410B69138D}" name="Tableau croisé dynamique1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:E10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -3150,22 +3178,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0AF269B-23FC-48D2-A16F-AEFC2A32B111}">
   <dimension ref="A1:I85"/>
-  <sheetFormatPr defaultColWidth="27.140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="27.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="54" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" style="64" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" style="53" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.7109375" style="65" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="54" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" style="64" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.6640625" style="65" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" style="54" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22" style="54" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="49.85546875" style="66" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="27.140625" style="54"/>
+    <col min="9" max="9" width="49.88671875" style="66" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="27.109375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1">
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="52"/>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
@@ -3176,20 +3204,20 @@
       <c r="H1" s="52"/>
       <c r="I1" s="52"/>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1">
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="52"/>
       <c r="B2" s="52"/>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
       <c r="F2" s="52"/>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
       <c r="I2" s="52"/>
     </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1">
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="52"/>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -3200,7 +3228,7 @@
       <c r="H3" s="52"/>
       <c r="I3" s="52"/>
     </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+    <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="52"/>
       <c r="B4" s="55" t="s">
         <v>1</v>
@@ -3227,7 +3255,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1">
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="52"/>
       <c r="B5" s="67" t="s">
         <v>9</v>
@@ -3254,7 +3282,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1">
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="52"/>
       <c r="B6" s="71">
         <v>27446</v>
@@ -3281,7 +3309,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1">
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="52"/>
       <c r="B7" s="76">
         <v>27933</v>
@@ -3308,7 +3336,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1">
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="52"/>
       <c r="B8" s="71">
         <v>28409</v>
@@ -3335,7 +3363,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1">
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="52"/>
       <c r="B9" s="76">
         <v>20055</v>
@@ -3362,7 +3390,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="52"/>
       <c r="B10" s="71">
         <v>28681</v>
@@ -3389,7 +3417,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1">
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="52"/>
       <c r="B11" s="76">
         <v>28941</v>
@@ -3416,7 +3444,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1">
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="52"/>
       <c r="B12" s="71">
         <v>29735</v>
@@ -3443,7 +3471,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1">
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="52"/>
       <c r="B13" s="76">
         <v>29741</v>
@@ -3470,7 +3498,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1">
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="52"/>
       <c r="B14" s="71">
         <v>30395</v>
@@ -3497,7 +3525,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1">
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="52"/>
       <c r="B15" s="78">
         <v>29076</v>
@@ -3524,7 +3552,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="52"/>
       <c r="B16" s="78">
         <v>31147</v>
@@ -3551,7 +3579,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="52"/>
       <c r="B17" s="76">
         <v>31359</v>
@@ -3578,7 +3606,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="52"/>
       <c r="B18" s="71">
         <v>31640</v>
@@ -3605,7 +3633,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="52"/>
       <c r="B19" s="76">
         <v>31955</v>
@@ -3632,7 +3660,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="52"/>
       <c r="B20" s="71">
         <v>31956</v>
@@ -3659,7 +3687,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="52"/>
       <c r="B21" s="76">
         <v>32125</v>
@@ -3686,7 +3714,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="52"/>
       <c r="B22" s="71">
         <v>32141</v>
@@ -3713,7 +3741,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="52"/>
       <c r="B23" s="76">
         <v>32228</v>
@@ -3740,7 +3768,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="52"/>
       <c r="B24" s="71">
         <v>32229</v>
@@ -3767,7 +3795,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="52"/>
       <c r="B25" s="76">
         <v>32226</v>
@@ -3794,7 +3822,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="52"/>
       <c r="B26" s="71">
         <v>32418</v>
@@ -3821,7 +3849,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="52"/>
       <c r="B27" s="76">
         <v>32425</v>
@@ -3848,7 +3876,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="52"/>
       <c r="B28" s="78">
         <v>32428</v>
@@ -3875,7 +3903,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="52"/>
       <c r="B29" s="78">
         <v>32277</v>
@@ -3902,7 +3930,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="52"/>
       <c r="B30" s="78">
         <v>32508</v>
@@ -3929,7 +3957,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1">
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="52"/>
       <c r="B31" s="78">
         <v>32427</v>
@@ -3956,7 +3984,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1">
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="52"/>
       <c r="B32" s="78">
         <v>32276</v>
@@ -3983,7 +4011,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1">
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="52"/>
       <c r="B33" s="78">
         <v>27932</v>
@@ -4010,7 +4038,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1">
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="52"/>
       <c r="B34" s="78">
         <v>33093</v>
@@ -4037,7 +4065,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1">
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="52"/>
       <c r="B35" s="76">
         <v>33156</v>
@@ -4064,7 +4092,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1">
+    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="52"/>
       <c r="B36" s="71">
         <v>33094</v>
@@ -4091,7 +4119,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" customHeight="1">
+    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="52"/>
       <c r="B37" s="76">
         <v>32930</v>
@@ -4118,7 +4146,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1">
+    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="52"/>
       <c r="B38" s="71">
         <v>33261</v>
@@ -4145,7 +4173,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15" customHeight="1">
+    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="52"/>
       <c r="B39" s="76">
         <v>33445</v>
@@ -4172,7 +4200,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15" customHeight="1">
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="52"/>
       <c r="B40" s="71">
         <v>31003</v>
@@ -4199,7 +4227,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15" customHeight="1">
+    <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="52"/>
       <c r="B41" s="76">
         <v>33627</v>
@@ -4226,7 +4254,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15" customHeight="1">
+    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="52"/>
       <c r="B42" s="71">
         <v>33558</v>
@@ -4253,7 +4281,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15" customHeight="1">
+    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="52"/>
       <c r="B43" s="76">
         <v>33576</v>
@@ -4280,7 +4308,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15" customHeight="1">
+    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="52"/>
       <c r="B44" s="71">
         <v>33577</v>
@@ -4307,7 +4335,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15" customHeight="1">
+    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="52"/>
       <c r="B45" s="76">
         <v>33574</v>
@@ -4334,7 +4362,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15" customHeight="1">
+    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="52"/>
       <c r="B46" s="71">
         <v>33579</v>
@@ -4361,7 +4389,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15" customHeight="1">
+    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="52"/>
       <c r="B47" s="76">
         <v>33575</v>
@@ -4388,7 +4416,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15" customHeight="1">
+    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="52"/>
       <c r="B48" s="71">
         <v>33778</v>
@@ -4415,7 +4443,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15" customHeight="1">
+    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="52"/>
       <c r="B49" s="76">
         <v>33578</v>
@@ -4442,7 +4470,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15" customHeight="1">
+    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="52"/>
       <c r="B50" s="78">
         <v>33719</v>
@@ -4469,7 +4497,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15" customHeight="1">
+    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="52"/>
       <c r="B51" s="78">
         <v>33568</v>
@@ -4496,7 +4524,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15" customHeight="1">
+    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="52"/>
       <c r="B52" s="78">
         <v>34093</v>
@@ -4523,7 +4551,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15" customHeight="1">
+    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="52"/>
       <c r="B53" s="78">
         <v>34092</v>
@@ -4550,7 +4578,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15" customHeight="1">
+    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="52"/>
       <c r="B54" s="71">
         <v>34144</v>
@@ -4577,7 +4605,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15" customHeight="1">
+    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="52"/>
       <c r="B55" s="76">
         <v>34169</v>
@@ -4604,7 +4632,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15" customHeight="1">
+    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="52"/>
       <c r="B56" s="71">
         <v>34167</v>
@@ -4631,7 +4659,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15" customHeight="1">
+    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="52"/>
       <c r="B57" s="76">
         <v>34168</v>
@@ -4658,7 +4686,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15" customHeight="1">
+    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="52"/>
       <c r="B58" s="71">
         <v>34200</v>
@@ -4685,7 +4713,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15" customHeight="1">
+    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="52"/>
       <c r="B59" s="76">
         <v>34213</v>
@@ -4712,7 +4740,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15" customHeight="1">
+    <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="52"/>
       <c r="B60" s="71">
         <v>34214</v>
@@ -4739,7 +4767,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15" customHeight="1">
+    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="52"/>
       <c r="B61" s="76">
         <v>34201</v>
@@ -4766,7 +4794,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15" customHeight="1">
+    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="52"/>
       <c r="B62" s="71">
         <v>34294</v>
@@ -4793,7 +4821,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15" customHeight="1">
+    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="52"/>
       <c r="B63" s="76">
         <v>34500</v>
@@ -4820,7 +4848,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15" customHeight="1">
+    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="52"/>
       <c r="B64" s="78">
         <v>34627</v>
@@ -4847,7 +4875,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" customHeight="1">
+    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="52"/>
       <c r="B65" s="78">
         <v>34626</v>
@@ -4874,7 +4902,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" customHeight="1">
+    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="52"/>
       <c r="B66" s="78">
         <v>34669</v>
@@ -4901,7 +4929,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15" customHeight="1">
+    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="52"/>
       <c r="B67" s="78">
         <v>34689</v>
@@ -4928,7 +4956,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15" customHeight="1">
+    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="52"/>
       <c r="B68" s="71">
         <v>34657</v>
@@ -4955,7 +4983,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15" customHeight="1">
+    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="52"/>
       <c r="B69" s="76">
         <v>34864</v>
@@ -4982,7 +5010,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15" customHeight="1">
+    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="52"/>
       <c r="B70" s="71">
         <v>34847</v>
@@ -5009,7 +5037,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15" customHeight="1">
+    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="52"/>
       <c r="B71" s="76">
         <v>34909</v>
@@ -5036,7 +5064,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15" customHeight="1">
+    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="52"/>
       <c r="B72" s="71">
         <v>34910</v>
@@ -5063,7 +5091,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15" customHeight="1">
+    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="52"/>
       <c r="B73" s="81">
         <v>35000</v>
@@ -5090,7 +5118,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15" customHeight="1">
+    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="52"/>
       <c r="B74" s="52"/>
       <c r="C74" s="52"/>
@@ -5101,7 +5129,7 @@
       <c r="H74" s="52"/>
       <c r="I74" s="52"/>
     </row>
-    <row r="75" spans="1:9" ht="15" customHeight="1">
+    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="52"/>
       <c r="B75" s="52"/>
       <c r="C75" s="52"/>
@@ -5112,7 +5140,7 @@
       <c r="H75" s="52"/>
       <c r="I75" s="52"/>
     </row>
-    <row r="76" spans="1:9" ht="15" customHeight="1">
+    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="52"/>
       <c r="B76" s="52"/>
       <c r="C76" s="52"/>
@@ -5123,7 +5151,7 @@
       <c r="H76" s="52"/>
       <c r="I76" s="52"/>
     </row>
-    <row r="77" spans="1:9" ht="15" customHeight="1">
+    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="52"/>
       <c r="B77" s="52"/>
       <c r="C77" s="52"/>
@@ -5134,7 +5162,7 @@
       <c r="H77" s="52"/>
       <c r="I77" s="52"/>
     </row>
-    <row r="78" spans="1:9" ht="15" customHeight="1">
+    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="52"/>
       <c r="B78" s="52"/>
       <c r="C78" s="52"/>
@@ -5145,7 +5173,7 @@
       <c r="H78" s="52"/>
       <c r="I78" s="52"/>
     </row>
-    <row r="79" spans="1:9" ht="15" customHeight="1">
+    <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="52"/>
       <c r="B79" s="52"/>
       <c r="C79" s="52"/>
@@ -5156,12 +5184,12 @@
       <c r="H79" s="52"/>
       <c r="I79" s="52"/>
     </row>
-    <row r="80" spans="1:9" ht="15" customHeight="1">
+    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="52"/>
-      <c r="B80" s="94" t="s">
+      <c r="B80" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="95"/>
+      <c r="C80" s="90"/>
       <c r="D80" s="52"/>
       <c r="E80" s="52"/>
       <c r="F80" s="52"/>
@@ -5169,7 +5197,7 @@
       <c r="H80" s="52"/>
       <c r="I80" s="52"/>
     </row>
-    <row r="81" spans="1:9" ht="15" customHeight="1">
+    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="52"/>
       <c r="B81" s="58" t="s">
         <v>20</v>
@@ -5184,7 +5212,7 @@
       <c r="H81" s="52"/>
       <c r="I81" s="52"/>
     </row>
-    <row r="82" spans="1:9" ht="15" customHeight="1">
+    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="52"/>
       <c r="B82" s="60" t="s">
         <v>36</v>
@@ -5199,7 +5227,7 @@
       <c r="H82" s="52"/>
       <c r="I82" s="52"/>
     </row>
-    <row r="83" spans="1:9" ht="15" customHeight="1">
+    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="52"/>
       <c r="B83" s="58" t="s">
         <v>45</v>
@@ -5214,7 +5242,7 @@
       <c r="H83" s="52"/>
       <c r="I83" s="52"/>
     </row>
-    <row r="84" spans="1:9" ht="15" customHeight="1">
+    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="52"/>
       <c r="B84" s="60" t="s">
         <v>127</v>
@@ -5229,7 +5257,7 @@
       <c r="H84" s="52"/>
       <c r="I84" s="52"/>
     </row>
-    <row r="85" spans="1:9" ht="15" customHeight="1">
+    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="52"/>
       <c r="B85" s="62" t="s">
         <v>25</v>
@@ -5260,7 +5288,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F596DFCD-A5A3-4AF6-95E4-F938251E06CC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5269,7 +5297,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B2DC9E1-0840-4F6B-8936-03950DB9D011}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5278,16 +5306,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD185231-ACFC-4ED8-BF5C-5C285BF0ABA2}">
   <dimension ref="A1:E64"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" customHeight="1">
+    <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
         <v>230</v>
       </c>
@@ -5304,7 +5332,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="38">
         <v>34864</v>
       </c>
@@ -5321,7 +5349,7 @@
         <v>568661342</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="42">
         <v>32427</v>
       </c>
@@ -5338,7 +5366,7 @@
         <v>582259125</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="38">
         <v>33778</v>
       </c>
@@ -5355,7 +5383,7 @@
         <v>537515155</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>34168</v>
       </c>
@@ -5372,7 +5400,7 @@
         <v>503544881</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>34669</v>
       </c>
@@ -5389,7 +5417,7 @@
         <v>562736115</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>32228</v>
       </c>
@@ -5406,7 +5434,7 @@
         <v>558995390</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>32428</v>
       </c>
@@ -5423,7 +5451,7 @@
         <v>564144621</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>34167</v>
       </c>
@@ -5440,7 +5468,7 @@
         <v>538186866</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="38">
         <v>33558</v>
       </c>
@@ -5457,7 +5485,7 @@
         <v>561170977</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>32125</v>
       </c>
@@ -5474,7 +5502,7 @@
         <v>508024634</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="38">
         <v>32141</v>
       </c>
@@ -5491,7 +5519,7 @@
         <v>594180850</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>33577</v>
       </c>
@@ -5508,7 +5536,7 @@
         <v>567667630</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="38">
         <v>31003</v>
       </c>
@@ -5525,7 +5553,7 @@
         <v>533153535</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>31956</v>
       </c>
@@ -5542,7 +5570,7 @@
         <v>598948116</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>34294</v>
       </c>
@@ -5559,7 +5587,7 @@
         <v>539196414</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>33574</v>
       </c>
@@ -5576,7 +5604,7 @@
         <v>554734943</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>34144</v>
       </c>
@@ -5593,7 +5621,7 @@
         <v>545100075</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>31640</v>
       </c>
@@ -5610,14 +5638,14 @@
         <v>545461564</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>34500</v>
       </c>
       <c r="B20" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="C20" s="93" t="s">
+      <c r="C20" s="88" t="s">
         <v>188</v>
       </c>
       <c r="D20" s="41" t="s">
@@ -5627,7 +5655,7 @@
         <v>531415743</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>32142</v>
       </c>
@@ -5644,7 +5672,7 @@
         <v>500502426</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>32930</v>
       </c>
@@ -5661,7 +5689,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>33578</v>
       </c>
@@ -5678,7 +5706,7 @@
         <v>501249779</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>32423</v>
       </c>
@@ -5695,7 +5723,7 @@
         <v>539674802</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>33093</v>
       </c>
@@ -5712,7 +5740,7 @@
         <v>546166237</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>27446</v>
       </c>
@@ -5729,7 +5757,7 @@
         <v>532926927</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>28941</v>
       </c>
@@ -5746,7 +5774,7 @@
         <v>532022999</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>29741</v>
       </c>
@@ -5763,7 +5791,7 @@
         <v>558183173</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>33579</v>
       </c>
@@ -5780,7 +5808,7 @@
         <v>508555012</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>32229</v>
       </c>
@@ -5797,7 +5825,7 @@
         <v>501070581</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>31359</v>
       </c>
@@ -5814,7 +5842,7 @@
         <v>560246352</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="38">
         <v>33575</v>
       </c>
@@ -5831,7 +5859,7 @@
         <v>550297736</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>29735</v>
       </c>
@@ -5848,7 +5876,7 @@
         <v>570362685</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>34169</v>
       </c>
@@ -5865,7 +5893,7 @@
         <v>530030386</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>27933</v>
       </c>
@@ -5882,7 +5910,7 @@
         <v>562072381</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>28409</v>
       </c>
@@ -5899,7 +5927,7 @@
         <v>546380314</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>32277</v>
       </c>
@@ -5916,7 +5944,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="38">
         <v>27932</v>
       </c>
@@ -5933,7 +5961,7 @@
         <v>545171528</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="42">
         <v>34093</v>
       </c>
@@ -5950,7 +5978,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="38">
         <v>34200</v>
       </c>
@@ -5967,7 +5995,7 @@
         <v>553033919</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>32226</v>
       </c>
@@ -5984,7 +6012,7 @@
         <v>534511299</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="38">
         <v>20055</v>
       </c>
@@ -6001,7 +6029,7 @@
         <v>535327320</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>29076</v>
       </c>
@@ -6018,7 +6046,7 @@
         <v>546386034</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="38">
         <v>33576</v>
       </c>
@@ -6035,7 +6063,7 @@
         <v>500745389</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>28681</v>
       </c>
@@ -6052,7 +6080,7 @@
         <v>566535577</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="38">
         <v>32418</v>
       </c>
@@ -6069,7 +6097,7 @@
         <v>530398929</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>32126</v>
       </c>
@@ -6086,7 +6114,7 @@
         <v>541372544</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="43" t="s">
         <v>9</v>
       </c>
@@ -6103,7 +6131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>34847</v>
       </c>
@@ -6120,7 +6148,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="38">
         <v>31955</v>
       </c>
@@ -6137,7 +6165,7 @@
         <v>551148108</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="38">
         <v>33156</v>
       </c>
@@ -6154,7 +6182,7 @@
         <v>563154384</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="38">
         <v>33719</v>
       </c>
@@ -6171,7 +6199,7 @@
         <v>548306419</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="38">
         <v>34092</v>
       </c>
@@ -6188,7 +6216,7 @@
         <v>530567110</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="42">
         <v>32276</v>
       </c>
@@ -6205,7 +6233,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="38">
         <v>33445</v>
       </c>
@@ -6222,7 +6250,7 @@
         <v>505292477</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="38">
         <v>34213</v>
       </c>
@@ -6239,7 +6267,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="38">
         <v>31147</v>
       </c>
@@ -6256,7 +6284,7 @@
         <v>536982071</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="38">
         <v>33094</v>
       </c>
@@ -6273,7 +6301,7 @@
         <v>580184755</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="42">
         <v>32828</v>
       </c>
@@ -6290,7 +6318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="42">
         <v>33568</v>
       </c>
@@ -6307,7 +6335,7 @@
         <v>500192594</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="38">
         <v>32425</v>
       </c>
@@ -6324,7 +6352,7 @@
         <v>537149786</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="38">
         <v>34689</v>
       </c>
@@ -6341,7 +6369,7 @@
         <v>535672392</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="38">
         <v>34909</v>
       </c>
@@ -6358,10 +6386,24 @@
         <v>551222341</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15"/>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="96">
+        <v>35092</v>
+      </c>
+      <c r="B64" t="s">
+        <v>355</v>
+      </c>
+      <c r="C64" s="97" t="s">
+        <v>356</v>
+      </c>
+      <c r="D64" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C20" r:id="rId1" xr:uid="{E9067DAE-307E-4DE5-9C07-6483F3D90ADA}"/>
+    <hyperlink ref="C64" r:id="rId2" xr:uid="{15B98ED2-9FBE-4C47-B8BF-B3BD25E93FF5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6370,17 +6412,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{887A3C45-2914-4BEF-A085-E8DA9CF84D43}">
   <dimension ref="A3:E10"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>304</v>
       </c>
@@ -6388,7 +6430,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
         <v>306</v>
       </c>
@@ -6405,7 +6447,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>311</v>
       </c>
@@ -6416,7 +6458,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>312</v>
       </c>
@@ -6427,7 +6469,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>313</v>
       </c>
@@ -6441,7 +6483,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>314</v>
       </c>
@@ -6452,12 +6494,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>310</v>
       </c>
@@ -6479,20 +6521,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A300AFEA-8914-478B-B995-C110AA1208AE}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="49.5" customHeight="1">
+    <row r="1" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>315</v>
       </c>
@@ -6502,20 +6544,20 @@
       <c r="C1" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="89" t="s">
+      <c r="D1" s="92" t="s">
         <v>318</v>
       </c>
-      <c r="E1" s="90"/>
+      <c r="E1" s="93"/>
       <c r="F1" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="G1" s="91" t="s">
+      <c r="G1" s="94" t="s">
         <v>320</v>
       </c>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>321</v>
       </c>
@@ -6525,10 +6567,10 @@
       <c r="C2" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="D2" s="92" t="s">
+      <c r="D2" s="95" t="s">
         <v>324</v>
       </c>
-      <c r="E2" s="92"/>
+      <c r="E2" s="95"/>
       <c r="F2" s="11" t="s">
         <v>325</v>
       </c>
@@ -6542,7 +6584,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -6561,7 +6603,7 @@
       </c>
       <c r="I3" s="15"/>
     </row>
-    <row r="4" spans="1:9" ht="15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>333</v>
       </c>
@@ -6588,7 +6630,7 @@
       </c>
       <c r="I4" s="21"/>
     </row>
-    <row r="5" spans="1:9" ht="15">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>337</v>
       </c>
@@ -6613,7 +6655,7 @@
       </c>
       <c r="I5" s="21"/>
     </row>
-    <row r="6" spans="1:9" ht="15">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="24"/>
       <c r="B6" s="17" t="s">
         <v>140</v>
@@ -6636,7 +6678,7 @@
       </c>
       <c r="I6" s="21"/>
     </row>
-    <row r="7" spans="1:9" ht="15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="24"/>
       <c r="B7" s="17" t="s">
         <v>159</v>
@@ -6653,7 +6695,7 @@
       </c>
       <c r="I7" s="21"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="24"/>
       <c r="B8" s="22"/>
       <c r="C8" s="23"/>
@@ -6668,7 +6710,7 @@
       </c>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G9" s="46" t="s">
         <v>149</v>
       </c>
@@ -6676,22 +6718,22 @@
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G10" s="1"/>
       <c r="H10" s="46" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G11" s="1"/>
       <c r="H11" s="47" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="87"/>
       <c r="C13" t="s">
         <v>349</v>
@@ -6741,15 +6783,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7325098A-1B83-4F7B-8AF7-9D6AF9F81E18}">
   <dimension ref="A2:E6"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="1" max="1" width="33.88671875" customWidth="1"/>
     <col min="2" max="2" width="50" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="48" customHeight="1">
+    <row r="2" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>350</v>
       </c>
@@ -6764,7 +6806,7 @@
       </c>
       <c r="E2" s="29"/>
     </row>
-    <row r="3" spans="1:5" ht="76.5" customHeight="1">
+    <row r="3" spans="1:5" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>15</v>
       </c>
@@ -6779,21 +6821,21 @@
       </c>
       <c r="E3" s="29"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="29"/>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
       <c r="E4" s="29"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="29"/>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
       <c r="D5" s="29"/>
       <c r="E5" s="29"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="29"/>
       <c r="B6" s="29"/>
       <c r="C6" s="29"/>
@@ -6806,6 +6848,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
+    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </hyperlink>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010057D8301AF2E034448D383AD6059623AD" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="010fb9c2226637447a522e2c91231dad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3491a11-7bba-4833-9e13-347a8af23878" xmlns:ns3="60327604-53ae-4893-9616-7899fcf99eb8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9c222462a19b0f1a46af5cffa3dc3b93" ns2:_="" ns3:_="">
     <xsd:import namespace="c3491a11-7bba-4833-9e13-347a8af23878"/>
@@ -7065,39 +7132,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
-    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </hyperlink>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD1400B-BCE6-4CA2-9823-1B96B380417C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
+    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD1400B-BCE6-4CA2-9823-1B96B380417C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
+    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/IDI_Team.xlsx
+++ b/IDI_Team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\rd6_generator_tool\rd6_deploy\rd6_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D1D883-A426-4227-935D-A0FD8E808670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE37CDEE-1E6B-44BF-BCF9-75D0AFC713AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5ABAA1C1-B119-44A8-8322-349E275CC8CB}"/>
   </bookViews>
@@ -1130,7 +1130,7 @@
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1212,13 +1212,21 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1226,46 +1234,46 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="12"/>
+      <color rgb="FF074F69"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
-      <color rgb="FF074F69"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
+      <sz val="12"/>
       <color rgb="FF0E2841"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="12"/>
       <color rgb="FFF1A983"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1656,7 +1664,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1785,106 +1793,133 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="18" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="17" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="17" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="18" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="17" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="17" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="18" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="18" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="10" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -3178,85 +3213,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0AF269B-23FC-48D2-A16F-AEFC2A32B111}">
   <dimension ref="A1:I85"/>
-  <sheetFormatPr defaultColWidth="27.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="27.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="54" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" style="64" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.6640625" style="65" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" style="54" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22" style="54" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="49.88671875" style="66" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="27.109375" style="54"/>
+    <col min="1" max="1" width="19.44140625" style="62" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" style="94" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.44140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.6640625" style="95" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" style="62" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22" style="62" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="49.88671875" style="96" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="27.109375" style="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="52"/>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="91" t="s">
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="61"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-    </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-    </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="52"/>
-      <c r="B4" s="55" t="s">
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="61"/>
+      <c r="B4" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="D4" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="56" t="s">
+      <c r="E4" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="56" t="s">
+      <c r="F4" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="56" t="s">
+      <c r="G4" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="56" t="s">
+      <c r="H4" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="57" t="s">
+      <c r="I4" s="66" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="52"/>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="61"/>
       <c r="B5" s="67" t="s">
         <v>9</v>
       </c>
@@ -3282,8 +3316,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="52"/>
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="61"/>
       <c r="B6" s="71">
         <v>27446</v>
       </c>
@@ -3309,8 +3343,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="52"/>
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="61"/>
       <c r="B7" s="76">
         <v>27933</v>
       </c>
@@ -3336,8 +3370,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="52"/>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="61"/>
       <c r="B8" s="71">
         <v>28409</v>
       </c>
@@ -3363,8 +3397,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="52"/>
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="61"/>
       <c r="B9" s="76">
         <v>20055</v>
       </c>
@@ -3390,8 +3424,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="52"/>
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="61"/>
       <c r="B10" s="71">
         <v>28681</v>
       </c>
@@ -3417,8 +3451,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="52"/>
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="61"/>
       <c r="B11" s="76">
         <v>28941</v>
       </c>
@@ -3444,8 +3478,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="52"/>
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="61"/>
       <c r="B12" s="71">
         <v>29735</v>
       </c>
@@ -3471,8 +3505,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="52"/>
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="61"/>
       <c r="B13" s="76">
         <v>29741</v>
       </c>
@@ -3494,12 +3528,12 @@
       <c r="H13" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="85" t="s">
+      <c r="I13" s="78" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="52"/>
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="61"/>
       <c r="B14" s="71">
         <v>30395</v>
       </c>
@@ -3525,9 +3559,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="52"/>
-      <c r="B15" s="78">
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="61"/>
+      <c r="B15" s="79">
         <v>29076</v>
       </c>
       <c r="C15" s="68" t="s">
@@ -3552,9 +3586,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="52"/>
-      <c r="B16" s="78">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="61"/>
+      <c r="B16" s="79">
         <v>31147</v>
       </c>
       <c r="C16" s="73" t="s">
@@ -3579,8 +3613,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="52"/>
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="61"/>
       <c r="B17" s="76">
         <v>31359</v>
       </c>
@@ -3606,8 +3640,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="52"/>
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="61"/>
       <c r="B18" s="71">
         <v>31640</v>
       </c>
@@ -3633,8 +3667,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="52"/>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="61"/>
       <c r="B19" s="76">
         <v>31955</v>
       </c>
@@ -3660,8 +3694,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="52"/>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="61"/>
       <c r="B20" s="71">
         <v>31956</v>
       </c>
@@ -3687,8 +3721,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="52"/>
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="61"/>
       <c r="B21" s="76">
         <v>32125</v>
       </c>
@@ -3714,8 +3748,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="52"/>
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="61"/>
       <c r="B22" s="71">
         <v>32141</v>
       </c>
@@ -3741,8 +3775,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="52"/>
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="61"/>
       <c r="B23" s="76">
         <v>32228</v>
       </c>
@@ -3768,8 +3802,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="52"/>
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="61"/>
       <c r="B24" s="71">
         <v>32229</v>
       </c>
@@ -3795,8 +3829,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="52"/>
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="61"/>
       <c r="B25" s="76">
         <v>32226</v>
       </c>
@@ -3822,8 +3856,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="52"/>
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="61"/>
       <c r="B26" s="71">
         <v>32418</v>
       </c>
@@ -3849,8 +3883,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="52"/>
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="61"/>
       <c r="B27" s="76">
         <v>32425</v>
       </c>
@@ -3876,9 +3910,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="52"/>
-      <c r="B28" s="78">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="61"/>
+      <c r="B28" s="79">
         <v>32428</v>
       </c>
       <c r="C28" s="72" t="s">
@@ -3903,9 +3937,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="52"/>
-      <c r="B29" s="78">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="61"/>
+      <c r="B29" s="79">
         <v>32277</v>
       </c>
       <c r="C29" s="77" t="s">
@@ -3930,9 +3964,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="52"/>
-      <c r="B30" s="78">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="61"/>
+      <c r="B30" s="79">
         <v>32508</v>
       </c>
       <c r="C30" s="73" t="s">
@@ -3957,9 +3991,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="52"/>
-      <c r="B31" s="78">
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="61"/>
+      <c r="B31" s="79">
         <v>32427</v>
       </c>
       <c r="C31" s="68" t="s">
@@ -3984,9 +4018,9 @@
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="52"/>
-      <c r="B32" s="78">
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="61"/>
+      <c r="B32" s="79">
         <v>32276</v>
       </c>
       <c r="C32" s="72" t="s">
@@ -4011,9 +4045,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="52"/>
-      <c r="B33" s="78">
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="61"/>
+      <c r="B33" s="79">
         <v>27932</v>
       </c>
       <c r="C33" s="68" t="s">
@@ -4038,9 +4072,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="52"/>
-      <c r="B34" s="78">
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="61"/>
+      <c r="B34" s="79">
         <v>33093</v>
       </c>
       <c r="C34" s="73" t="s">
@@ -4065,8 +4099,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="52"/>
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="61"/>
       <c r="B35" s="76">
         <v>33156</v>
       </c>
@@ -4092,8 +4126,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="52"/>
+    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="61"/>
       <c r="B36" s="71">
         <v>33094</v>
       </c>
@@ -4119,8 +4153,8 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="52"/>
+    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="61"/>
       <c r="B37" s="76">
         <v>32930</v>
       </c>
@@ -4146,8 +4180,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="52"/>
+    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="61"/>
       <c r="B38" s="71">
         <v>33261</v>
       </c>
@@ -4173,8 +4207,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="52"/>
+    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="61"/>
       <c r="B39" s="76">
         <v>33445</v>
       </c>
@@ -4200,8 +4234,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="52"/>
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="61"/>
       <c r="B40" s="71">
         <v>31003</v>
       </c>
@@ -4227,8 +4261,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="52"/>
+    <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="61"/>
       <c r="B41" s="76">
         <v>33627</v>
       </c>
@@ -4254,8 +4288,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="52"/>
+    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="61"/>
       <c r="B42" s="71">
         <v>33558</v>
       </c>
@@ -4281,8 +4315,8 @@
         <v>134</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="52"/>
+    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="61"/>
       <c r="B43" s="76">
         <v>33576</v>
       </c>
@@ -4308,8 +4342,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="52"/>
+    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="61"/>
       <c r="B44" s="71">
         <v>33577</v>
       </c>
@@ -4335,8 +4369,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="52"/>
+    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="61"/>
       <c r="B45" s="76">
         <v>33574</v>
       </c>
@@ -4362,8 +4396,8 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="52"/>
+    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="61"/>
       <c r="B46" s="71">
         <v>33579</v>
       </c>
@@ -4389,8 +4423,8 @@
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="52"/>
+    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="61"/>
       <c r="B47" s="76">
         <v>33575</v>
       </c>
@@ -4416,8 +4450,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="52"/>
+    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="61"/>
       <c r="B48" s="71">
         <v>33778</v>
       </c>
@@ -4443,8 +4477,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="52"/>
+    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="61"/>
       <c r="B49" s="76">
         <v>33578</v>
       </c>
@@ -4470,9 +4504,9 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="52"/>
-      <c r="B50" s="78">
+    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="61"/>
+      <c r="B50" s="79">
         <v>33719</v>
       </c>
       <c r="C50" s="73" t="s">
@@ -4497,9 +4531,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="52"/>
-      <c r="B51" s="78">
+    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="61"/>
+      <c r="B51" s="79">
         <v>33568</v>
       </c>
       <c r="C51" s="68" t="s">
@@ -4524,9 +4558,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="52"/>
-      <c r="B52" s="78">
+    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="61"/>
+      <c r="B52" s="79">
         <v>34093</v>
       </c>
       <c r="C52" s="73" t="s">
@@ -4551,9 +4585,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="52"/>
-      <c r="B53" s="78">
+    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="61"/>
+      <c r="B53" s="79">
         <v>34092</v>
       </c>
       <c r="C53" s="68" t="s">
@@ -4578,8 +4612,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="52"/>
+    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="61"/>
       <c r="B54" s="71">
         <v>34144</v>
       </c>
@@ -4605,8 +4639,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="52"/>
+    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="61"/>
       <c r="B55" s="76">
         <v>34169</v>
       </c>
@@ -4632,8 +4666,8 @@
         <v>167</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="52"/>
+    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="61"/>
       <c r="B56" s="71">
         <v>34167</v>
       </c>
@@ -4659,8 +4693,8 @@
         <v>169</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="52"/>
+    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="61"/>
       <c r="B57" s="76">
         <v>34168</v>
       </c>
@@ -4686,8 +4720,8 @@
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="52"/>
+    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="61"/>
       <c r="B58" s="71">
         <v>34200</v>
       </c>
@@ -4713,8 +4747,8 @@
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="52"/>
+    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="61"/>
       <c r="B59" s="76">
         <v>34213</v>
       </c>
@@ -4740,8 +4774,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="52"/>
+    <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="61"/>
       <c r="B60" s="71">
         <v>34214</v>
       </c>
@@ -4767,8 +4801,8 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="52"/>
+    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="61"/>
       <c r="B61" s="76">
         <v>34201</v>
       </c>
@@ -4794,8 +4828,8 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="52"/>
+    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="61"/>
       <c r="B62" s="71">
         <v>34294</v>
       </c>
@@ -4821,8 +4855,8 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="52"/>
+    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="61"/>
       <c r="B63" s="76">
         <v>34500</v>
       </c>
@@ -4848,9 +4882,9 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="52"/>
-      <c r="B64" s="78">
+    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="61"/>
+      <c r="B64" s="79">
         <v>34627</v>
       </c>
       <c r="C64" s="73" t="s">
@@ -4865,7 +4899,7 @@
       <c r="F64" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="G64" s="79">
+      <c r="G64" s="80">
         <v>45963</v>
       </c>
       <c r="H64" s="73" t="s">
@@ -4875,9 +4909,9 @@
         <v>192</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="52"/>
-      <c r="B65" s="78">
+    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="61"/>
+      <c r="B65" s="79">
         <v>34626</v>
       </c>
       <c r="C65" s="68" t="s">
@@ -4892,7 +4926,7 @@
       <c r="F65" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G65" s="79">
+      <c r="G65" s="80">
         <v>45965</v>
       </c>
       <c r="H65" s="68" t="s">
@@ -4902,9 +4936,9 @@
         <v>196</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="52"/>
-      <c r="B66" s="78">
+    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="61"/>
+      <c r="B66" s="79">
         <v>34669</v>
       </c>
       <c r="C66" s="73" t="s">
@@ -4919,7 +4953,7 @@
       <c r="F66" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="G66" s="79">
+      <c r="G66" s="80">
         <v>45970</v>
       </c>
       <c r="H66" s="73" t="s">
@@ -4929,9 +4963,9 @@
         <v>199</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="52"/>
-      <c r="B67" s="78">
+    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="61"/>
+      <c r="B67" s="79">
         <v>34689</v>
       </c>
       <c r="C67" s="68" t="s">
@@ -4946,7 +4980,7 @@
       <c r="F67" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="G67" s="79">
+      <c r="G67" s="80">
         <v>45977</v>
       </c>
       <c r="H67" s="68" t="s">
@@ -4956,8 +4990,8 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="52"/>
+    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="61"/>
       <c r="B68" s="71">
         <v>34657</v>
       </c>
@@ -4983,8 +5017,8 @@
         <v>206</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="52"/>
+    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="61"/>
       <c r="B69" s="76">
         <v>34864</v>
       </c>
@@ -5010,8 +5044,8 @@
         <v>210</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="52"/>
+    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="61"/>
       <c r="B70" s="71">
         <v>34847</v>
       </c>
@@ -5037,12 +5071,12 @@
         <v>213</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="52"/>
+    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="61"/>
       <c r="B71" s="76">
         <v>34909</v>
       </c>
-      <c r="C71" s="80" t="s">
+      <c r="C71" s="81" t="s">
         <v>214</v>
       </c>
       <c r="D71" s="68" t="s">
@@ -5064,12 +5098,12 @@
         <v>217</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="52"/>
+    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="61"/>
       <c r="B72" s="71">
         <v>34910</v>
       </c>
-      <c r="C72" s="80" t="s">
+      <c r="C72" s="81" t="s">
         <v>218</v>
       </c>
       <c r="D72" s="73" t="s">
@@ -5091,186 +5125,186 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="52"/>
-      <c r="B73" s="81">
+    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="61"/>
+      <c r="B73" s="82">
         <v>35000</v>
       </c>
-      <c r="C73" s="82" t="s">
+      <c r="C73" s="83" t="s">
         <v>222</v>
       </c>
-      <c r="D73" s="82" t="s">
+      <c r="D73" s="83" t="s">
         <v>223</v>
       </c>
-      <c r="E73" s="82" t="s">
-        <v>44</v>
-      </c>
-      <c r="F73" s="82" t="s">
+      <c r="E73" s="83" t="s">
+        <v>44</v>
+      </c>
+      <c r="F73" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="G73" s="83">
+      <c r="G73" s="84">
         <v>46047</v>
       </c>
-      <c r="H73" s="82" t="s">
+      <c r="H73" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="I73" s="84" t="s">
+      <c r="I73" s="85" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="52"/>
-      <c r="B74" s="52"/>
-      <c r="C74" s="52"/>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
-      <c r="G74" s="52"/>
-      <c r="H74" s="52"/>
-      <c r="I74" s="52"/>
-    </row>
-    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="52"/>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
-    </row>
-    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
-    </row>
-    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="52"/>
-      <c r="B77" s="52"/>
-      <c r="C77" s="52"/>
-      <c r="D77" s="52"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="52"/>
-      <c r="G77" s="52"/>
-      <c r="H77" s="52"/>
-      <c r="I77" s="52"/>
-    </row>
-    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="52"/>
-      <c r="B78" s="52"/>
-      <c r="C78" s="52"/>
-      <c r="D78" s="52"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
-      <c r="G78" s="52"/>
-      <c r="H78" s="52"/>
-      <c r="I78" s="52"/>
-    </row>
-    <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="52"/>
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
-      <c r="I79" s="52"/>
-    </row>
-    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="52"/>
-      <c r="B80" s="89" t="s">
+    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="61"/>
+      <c r="B74" s="61"/>
+      <c r="C74" s="61"/>
+      <c r="D74" s="61"/>
+      <c r="E74" s="61"/>
+      <c r="F74" s="61"/>
+      <c r="G74" s="61"/>
+      <c r="H74" s="61"/>
+      <c r="I74" s="61"/>
+    </row>
+    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="61"/>
+      <c r="B75" s="61"/>
+      <c r="C75" s="61"/>
+      <c r="D75" s="61"/>
+      <c r="E75" s="61"/>
+      <c r="F75" s="61"/>
+      <c r="G75" s="61"/>
+      <c r="H75" s="61"/>
+      <c r="I75" s="61"/>
+    </row>
+    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="61"/>
+      <c r="B76" s="61"/>
+      <c r="C76" s="61"/>
+      <c r="D76" s="61"/>
+      <c r="E76" s="61"/>
+      <c r="F76" s="61"/>
+      <c r="G76" s="61"/>
+      <c r="H76" s="61"/>
+      <c r="I76" s="61"/>
+    </row>
+    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="61"/>
+      <c r="B77" s="61"/>
+      <c r="C77" s="61"/>
+      <c r="D77" s="61"/>
+      <c r="E77" s="61"/>
+      <c r="F77" s="61"/>
+      <c r="G77" s="61"/>
+      <c r="H77" s="61"/>
+      <c r="I77" s="61"/>
+    </row>
+    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="61"/>
+      <c r="B78" s="61"/>
+      <c r="C78" s="61"/>
+      <c r="D78" s="61"/>
+      <c r="E78" s="61"/>
+      <c r="F78" s="61"/>
+      <c r="G78" s="61"/>
+      <c r="H78" s="61"/>
+      <c r="I78" s="61"/>
+    </row>
+    <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="61"/>
+      <c r="B79" s="61"/>
+      <c r="C79" s="61"/>
+      <c r="D79" s="61"/>
+      <c r="E79" s="61"/>
+      <c r="F79" s="61"/>
+      <c r="G79" s="61"/>
+      <c r="H79" s="61"/>
+      <c r="I79" s="61"/>
+    </row>
+    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="61"/>
+      <c r="B80" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="90"/>
-      <c r="D80" s="52"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
-      <c r="G80" s="52"/>
-      <c r="H80" s="52"/>
-      <c r="I80" s="52"/>
-    </row>
-    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="52"/>
-      <c r="B81" s="58" t="s">
+      <c r="C80" s="87"/>
+      <c r="D80" s="61"/>
+      <c r="E80" s="61"/>
+      <c r="F80" s="61"/>
+      <c r="G80" s="61"/>
+      <c r="H80" s="61"/>
+      <c r="I80" s="61"/>
+    </row>
+    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="61"/>
+      <c r="B81" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="C81" s="59" t="s">
+      <c r="C81" s="89" t="s">
         <v>225</v>
       </c>
-      <c r="D81" s="52"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="52"/>
-      <c r="G81" s="52"/>
-      <c r="H81" s="52"/>
-      <c r="I81" s="52"/>
-    </row>
-    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="52"/>
-      <c r="B82" s="60" t="s">
+      <c r="D81" s="61"/>
+      <c r="E81" s="61"/>
+      <c r="F81" s="61"/>
+      <c r="G81" s="61"/>
+      <c r="H81" s="61"/>
+      <c r="I81" s="61"/>
+    </row>
+    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="61"/>
+      <c r="B82" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="C82" s="61" t="s">
+      <c r="C82" s="91" t="s">
         <v>226</v>
       </c>
-      <c r="D82" s="52"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="52"/>
-      <c r="G82" s="52"/>
-      <c r="H82" s="52"/>
-      <c r="I82" s="52"/>
-    </row>
-    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="52"/>
-      <c r="B83" s="58" t="s">
+      <c r="D82" s="61"/>
+      <c r="E82" s="61"/>
+      <c r="F82" s="61"/>
+      <c r="G82" s="61"/>
+      <c r="H82" s="61"/>
+      <c r="I82" s="61"/>
+    </row>
+    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="61"/>
+      <c r="B83" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="C83" s="59" t="s">
+      <c r="C83" s="89" t="s">
         <v>227</v>
       </c>
-      <c r="D83" s="52"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="52"/>
-      <c r="G83" s="52"/>
-      <c r="H83" s="52"/>
-      <c r="I83" s="52"/>
-    </row>
-    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="52"/>
-      <c r="B84" s="60" t="s">
+      <c r="D83" s="61"/>
+      <c r="E83" s="61"/>
+      <c r="F83" s="61"/>
+      <c r="G83" s="61"/>
+      <c r="H83" s="61"/>
+      <c r="I83" s="61"/>
+    </row>
+    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="61"/>
+      <c r="B84" s="90" t="s">
         <v>127</v>
       </c>
-      <c r="C84" s="61" t="s">
+      <c r="C84" s="91" t="s">
         <v>228</v>
       </c>
-      <c r="D84" s="52"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="52"/>
-      <c r="G84" s="52"/>
-      <c r="H84" s="52"/>
-      <c r="I84" s="52"/>
-    </row>
-    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="52"/>
-      <c r="B85" s="62" t="s">
+      <c r="D84" s="61"/>
+      <c r="E84" s="61"/>
+      <c r="F84" s="61"/>
+      <c r="G84" s="61"/>
+      <c r="H84" s="61"/>
+      <c r="I84" s="61"/>
+    </row>
+    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="61"/>
+      <c r="B85" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="C85" s="63" t="s">
+      <c r="C85" s="93" t="s">
         <v>229</v>
       </c>
-      <c r="D85" s="52"/>
-      <c r="E85" s="52"/>
-      <c r="F85" s="52"/>
-      <c r="G85" s="52"/>
-      <c r="H85" s="52"/>
-      <c r="I85" s="52"/>
+      <c r="D85" s="61"/>
+      <c r="E85" s="61"/>
+      <c r="F85" s="61"/>
+      <c r="G85" s="61"/>
+      <c r="H85" s="61"/>
+      <c r="I85" s="61"/>
     </row>
   </sheetData>
   <autoFilter ref="H1:H85" xr:uid="{C0AF269B-23FC-48D2-A16F-AEFC2A32B111}"/>
@@ -5645,7 +5679,7 @@
       <c r="B20" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="C20" s="88" t="s">
+      <c r="C20" s="54" t="s">
         <v>188</v>
       </c>
       <c r="D20" s="41" t="s">
@@ -6387,13 +6421,13 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="96">
+      <c r="A64" s="55">
         <v>35092</v>
       </c>
       <c r="B64" t="s">
         <v>355</v>
       </c>
-      <c r="C64" s="97" t="s">
+      <c r="C64" s="56" t="s">
         <v>356</v>
       </c>
       <c r="D64" s="41" t="s">
@@ -6544,18 +6578,18 @@
       <c r="C1" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="92" t="s">
+      <c r="D1" s="57" t="s">
         <v>318</v>
       </c>
-      <c r="E1" s="93"/>
+      <c r="E1" s="58"/>
       <c r="F1" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="G1" s="94" t="s">
+      <c r="G1" s="59" t="s">
         <v>320</v>
       </c>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -6567,10 +6601,10 @@
       <c r="C2" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="D2" s="95" t="s">
+      <c r="D2" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="E2" s="95"/>
+      <c r="E2" s="60"/>
       <c r="F2" s="11" t="s">
         <v>325</v>
       </c>
@@ -6650,7 +6684,7 @@
       <c r="G5" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="H5" s="86" t="s">
+      <c r="H5" s="52" t="s">
         <v>341</v>
       </c>
       <c r="I5" s="21"/>
@@ -6670,7 +6704,7 @@
       <c r="F6" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="G6" s="86" t="s">
+      <c r="G6" s="52" t="s">
         <v>344</v>
       </c>
       <c r="H6" s="21" t="s">
@@ -6734,7 +6768,7 @@
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="87"/>
+      <c r="B13" s="53"/>
       <c r="C13" t="s">
         <v>349</v>
       </c>
@@ -6857,22 +6891,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
-    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </hyperlink>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010057D8301AF2E034448D383AD6059623AD" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="010fb9c2226637447a522e2c91231dad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3491a11-7bba-4833-9e13-347a8af23878" xmlns:ns3="60327604-53ae-4893-9616-7899fcf99eb8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9c222462a19b0f1a46af5cffa3dc3b93" ns2:_="" ns3:_="">
     <xsd:import namespace="c3491a11-7bba-4833-9e13-347a8af23878"/>
@@ -7132,6 +7150,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
+    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </hyperlink>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
   <ds:schemaRefs>
@@ -7141,17 +7175,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
-    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD1400B-BCE6-4CA2-9823-1B96B380417C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7168,4 +7191,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
+    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/IDI_Team.xlsx
+++ b/IDI_Team.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\rd6_generator_tool\rd6_deploy\rd6_tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\rd6_generator_tool\rd6_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE37CDEE-1E6B-44BF-BCF9-75D0AFC713AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652225D0-F53F-4F2D-9D8A-14179060BE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5ABAA1C1-B119-44A8-8322-349E275CC8CB}"/>
   </bookViews>
@@ -17,16 +17,17 @@
     <sheet name="IDI" sheetId="6" r:id="rId2"/>
     <sheet name="Admin" sheetId="7" r:id="rId3"/>
     <sheet name="ENGs" sheetId="5" r:id="rId4"/>
-    <sheet name="Nbr-branch" sheetId="3" r:id="rId5"/>
-    <sheet name="Tech Leads" sheetId="2" r:id="rId6"/>
-    <sheet name="By branch" sheetId="4" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId5"/>
+    <sheet name="Nbr-branch" sheetId="3" r:id="rId6"/>
+    <sheet name="Tech Leads" sheetId="2" r:id="rId7"/>
+    <sheet name="By branch" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Current Staff'!$H$1:$H$85</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="362">
   <si>
     <t>KSA STAFF</t>
   </si>
@@ -1116,10 +1117,25 @@
     <t>25 (including HR, Accounting, Quality, IT &amp; office boy)</t>
   </si>
   <si>
-    <t>Ali KAMAL</t>
-  </si>
-  <si>
-    <t>ali.kamal@socotec.com</t>
+    <t>Bader ORAINI</t>
+  </si>
+  <si>
+    <t>50 380 9977</t>
+  </si>
+  <si>
+    <t>Technical Team Lead</t>
+  </si>
+  <si>
+    <t>Deputy Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOCOTEC IDI Riyadh (Central Region) </t>
+  </si>
+  <si>
+    <t>ayman.ashraf@socotec.com</t>
+  </si>
+  <si>
+    <t>Ayman ASHRAF</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1146,7 @@
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1212,21 +1228,13 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1234,46 +1242,46 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
       <color rgb="FF074F69"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="16"/>
       <color rgb="FF0E2841"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="16"/>
       <color rgb="FFF1A983"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1664,7 +1672,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1793,13 +1801,129 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="18" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="18" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="18" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="18" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="10" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1812,114 +1936,9 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="17" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="17" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="17" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="17" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -3213,84 +3232,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0AF269B-23FC-48D2-A16F-AEFC2A32B111}">
   <dimension ref="A1:I85"/>
-  <sheetFormatPr defaultColWidth="27.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="27.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="62" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" style="94" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.44140625" style="62" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.6640625" style="95" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" style="62" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" style="62" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22" style="62" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="49.88671875" style="96" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.109375" style="62" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="27.109375" style="62"/>
+    <col min="1" max="1" width="19.44140625" style="54" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" style="64" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.6640625" style="65" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" style="54" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22" style="54" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="49.88671875" style="66" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="27.109375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="61"/>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="63" t="s">
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="52"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-    </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="61"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-    </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="61"/>
-      <c r="B4" s="64" t="s">
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="52"/>
+      <c r="B4" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="65" t="s">
+      <c r="C4" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="E4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="65" t="s">
+      <c r="F4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="65" t="s">
+      <c r="H4" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="66" t="s">
+      <c r="I4" s="57" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="61"/>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="52"/>
       <c r="B5" s="67" t="s">
         <v>9</v>
       </c>
@@ -3316,8 +3336,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="61"/>
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="52"/>
       <c r="B6" s="71">
         <v>27446</v>
       </c>
@@ -3343,8 +3363,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="61"/>
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="52"/>
       <c r="B7" s="76">
         <v>27933</v>
       </c>
@@ -3370,8 +3390,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="61"/>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="52"/>
       <c r="B8" s="71">
         <v>28409</v>
       </c>
@@ -3397,8 +3417,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="61"/>
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="52"/>
       <c r="B9" s="76">
         <v>20055</v>
       </c>
@@ -3424,8 +3444,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="61"/>
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="52"/>
       <c r="B10" s="71">
         <v>28681</v>
       </c>
@@ -3451,8 +3471,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="61"/>
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="52"/>
       <c r="B11" s="76">
         <v>28941</v>
       </c>
@@ -3478,8 +3498,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="61"/>
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="52"/>
       <c r="B12" s="71">
         <v>29735</v>
       </c>
@@ -3505,8 +3525,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="61"/>
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="52"/>
       <c r="B13" s="76">
         <v>29741</v>
       </c>
@@ -3528,12 +3548,12 @@
       <c r="H13" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="78" t="s">
+      <c r="I13" s="85" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="61"/>
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="52"/>
       <c r="B14" s="71">
         <v>30395</v>
       </c>
@@ -3559,9 +3579,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="61"/>
-      <c r="B15" s="79">
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="52"/>
+      <c r="B15" s="78">
         <v>29076</v>
       </c>
       <c r="C15" s="68" t="s">
@@ -3586,9 +3606,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="61"/>
-      <c r="B16" s="79">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="52"/>
+      <c r="B16" s="78">
         <v>31147</v>
       </c>
       <c r="C16" s="73" t="s">
@@ -3613,8 +3633,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="61"/>
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="52"/>
       <c r="B17" s="76">
         <v>31359</v>
       </c>
@@ -3640,8 +3660,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="61"/>
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="52"/>
       <c r="B18" s="71">
         <v>31640</v>
       </c>
@@ -3667,8 +3687,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="61"/>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="52"/>
       <c r="B19" s="76">
         <v>31955</v>
       </c>
@@ -3694,8 +3714,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="61"/>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="52"/>
       <c r="B20" s="71">
         <v>31956</v>
       </c>
@@ -3721,8 +3741,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="61"/>
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="52"/>
       <c r="B21" s="76">
         <v>32125</v>
       </c>
@@ -3748,8 +3768,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="61"/>
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="52"/>
       <c r="B22" s="71">
         <v>32141</v>
       </c>
@@ -3775,8 +3795,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="61"/>
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="52"/>
       <c r="B23" s="76">
         <v>32228</v>
       </c>
@@ -3802,8 +3822,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="61"/>
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="52"/>
       <c r="B24" s="71">
         <v>32229</v>
       </c>
@@ -3829,8 +3849,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="61"/>
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="52"/>
       <c r="B25" s="76">
         <v>32226</v>
       </c>
@@ -3856,8 +3876,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="61"/>
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="52"/>
       <c r="B26" s="71">
         <v>32418</v>
       </c>
@@ -3883,8 +3903,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="61"/>
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="52"/>
       <c r="B27" s="76">
         <v>32425</v>
       </c>
@@ -3910,9 +3930,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="61"/>
-      <c r="B28" s="79">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="52"/>
+      <c r="B28" s="78">
         <v>32428</v>
       </c>
       <c r="C28" s="72" t="s">
@@ -3937,9 +3957,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="61"/>
-      <c r="B29" s="79">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="52"/>
+      <c r="B29" s="78">
         <v>32277</v>
       </c>
       <c r="C29" s="77" t="s">
@@ -3964,9 +3984,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="61"/>
-      <c r="B30" s="79">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="52"/>
+      <c r="B30" s="78">
         <v>32508</v>
       </c>
       <c r="C30" s="73" t="s">
@@ -3991,9 +4011,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="61"/>
-      <c r="B31" s="79">
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="52"/>
+      <c r="B31" s="78">
         <v>32427</v>
       </c>
       <c r="C31" s="68" t="s">
@@ -4018,9 +4038,9 @@
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="61"/>
-      <c r="B32" s="79">
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="52"/>
+      <c r="B32" s="78">
         <v>32276</v>
       </c>
       <c r="C32" s="72" t="s">
@@ -4045,9 +4065,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="61"/>
-      <c r="B33" s="79">
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="52"/>
+      <c r="B33" s="78">
         <v>27932</v>
       </c>
       <c r="C33" s="68" t="s">
@@ -4072,9 +4092,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="61"/>
-      <c r="B34" s="79">
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="52"/>
+      <c r="B34" s="78">
         <v>33093</v>
       </c>
       <c r="C34" s="73" t="s">
@@ -4099,8 +4119,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="61"/>
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="52"/>
       <c r="B35" s="76">
         <v>33156</v>
       </c>
@@ -4126,8 +4146,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="61"/>
+    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="52"/>
       <c r="B36" s="71">
         <v>33094</v>
       </c>
@@ -4153,8 +4173,8 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="61"/>
+    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="52"/>
       <c r="B37" s="76">
         <v>32930</v>
       </c>
@@ -4180,8 +4200,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="61"/>
+    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="52"/>
       <c r="B38" s="71">
         <v>33261</v>
       </c>
@@ -4207,8 +4227,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="61"/>
+    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="52"/>
       <c r="B39" s="76">
         <v>33445</v>
       </c>
@@ -4234,8 +4254,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="61"/>
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="52"/>
       <c r="B40" s="71">
         <v>31003</v>
       </c>
@@ -4261,8 +4281,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="61"/>
+    <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="52"/>
       <c r="B41" s="76">
         <v>33627</v>
       </c>
@@ -4288,8 +4308,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="61"/>
+    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="52"/>
       <c r="B42" s="71">
         <v>33558</v>
       </c>
@@ -4315,8 +4335,8 @@
         <v>134</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="61"/>
+    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="52"/>
       <c r="B43" s="76">
         <v>33576</v>
       </c>
@@ -4342,8 +4362,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="61"/>
+    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="52"/>
       <c r="B44" s="71">
         <v>33577</v>
       </c>
@@ -4369,8 +4389,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="61"/>
+    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="52"/>
       <c r="B45" s="76">
         <v>33574</v>
       </c>
@@ -4396,8 +4416,8 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="61"/>
+    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="52"/>
       <c r="B46" s="71">
         <v>33579</v>
       </c>
@@ -4423,8 +4443,8 @@
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="61"/>
+    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="52"/>
       <c r="B47" s="76">
         <v>33575</v>
       </c>
@@ -4450,8 +4470,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="61"/>
+    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="52"/>
       <c r="B48" s="71">
         <v>33778</v>
       </c>
@@ -4477,8 +4497,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="61"/>
+    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="52"/>
       <c r="B49" s="76">
         <v>33578</v>
       </c>
@@ -4504,9 +4524,9 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="61"/>
-      <c r="B50" s="79">
+    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="52"/>
+      <c r="B50" s="78">
         <v>33719</v>
       </c>
       <c r="C50" s="73" t="s">
@@ -4531,9 +4551,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="61"/>
-      <c r="B51" s="79">
+    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="52"/>
+      <c r="B51" s="78">
         <v>33568</v>
       </c>
       <c r="C51" s="68" t="s">
@@ -4558,9 +4578,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="61"/>
-      <c r="B52" s="79">
+    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="52"/>
+      <c r="B52" s="78">
         <v>34093</v>
       </c>
       <c r="C52" s="73" t="s">
@@ -4585,9 +4605,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="61"/>
-      <c r="B53" s="79">
+    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="52"/>
+      <c r="B53" s="78">
         <v>34092</v>
       </c>
       <c r="C53" s="68" t="s">
@@ -4612,8 +4632,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="61"/>
+    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="52"/>
       <c r="B54" s="71">
         <v>34144</v>
       </c>
@@ -4639,8 +4659,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="61"/>
+    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="52"/>
       <c r="B55" s="76">
         <v>34169</v>
       </c>
@@ -4666,8 +4686,8 @@
         <v>167</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="61"/>
+    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="52"/>
       <c r="B56" s="71">
         <v>34167</v>
       </c>
@@ -4693,8 +4713,8 @@
         <v>169</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="61"/>
+    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="52"/>
       <c r="B57" s="76">
         <v>34168</v>
       </c>
@@ -4720,8 +4740,8 @@
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="61"/>
+    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="52"/>
       <c r="B58" s="71">
         <v>34200</v>
       </c>
@@ -4747,8 +4767,8 @@
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="61"/>
+    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="52"/>
       <c r="B59" s="76">
         <v>34213</v>
       </c>
@@ -4774,8 +4794,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="61"/>
+    <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="52"/>
       <c r="B60" s="71">
         <v>34214</v>
       </c>
@@ -4801,8 +4821,8 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="61"/>
+    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="52"/>
       <c r="B61" s="76">
         <v>34201</v>
       </c>
@@ -4828,8 +4848,8 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="61"/>
+    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="52"/>
       <c r="B62" s="71">
         <v>34294</v>
       </c>
@@ -4855,8 +4875,8 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="61"/>
+    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="52"/>
       <c r="B63" s="76">
         <v>34500</v>
       </c>
@@ -4882,9 +4902,9 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="61"/>
-      <c r="B64" s="79">
+    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="52"/>
+      <c r="B64" s="78">
         <v>34627</v>
       </c>
       <c r="C64" s="73" t="s">
@@ -4899,7 +4919,7 @@
       <c r="F64" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="G64" s="80">
+      <c r="G64" s="79">
         <v>45963</v>
       </c>
       <c r="H64" s="73" t="s">
@@ -4909,9 +4929,9 @@
         <v>192</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="61"/>
-      <c r="B65" s="79">
+    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="52"/>
+      <c r="B65" s="78">
         <v>34626</v>
       </c>
       <c r="C65" s="68" t="s">
@@ -4926,7 +4946,7 @@
       <c r="F65" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G65" s="80">
+      <c r="G65" s="79">
         <v>45965</v>
       </c>
       <c r="H65" s="68" t="s">
@@ -4936,9 +4956,9 @@
         <v>196</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="61"/>
-      <c r="B66" s="79">
+    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="52"/>
+      <c r="B66" s="78">
         <v>34669</v>
       </c>
       <c r="C66" s="73" t="s">
@@ -4953,7 +4973,7 @@
       <c r="F66" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="G66" s="80">
+      <c r="G66" s="79">
         <v>45970</v>
       </c>
       <c r="H66" s="73" t="s">
@@ -4963,9 +4983,9 @@
         <v>199</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="61"/>
-      <c r="B67" s="79">
+    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="52"/>
+      <c r="B67" s="78">
         <v>34689</v>
       </c>
       <c r="C67" s="68" t="s">
@@ -4980,7 +5000,7 @@
       <c r="F67" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="G67" s="80">
+      <c r="G67" s="79">
         <v>45977</v>
       </c>
       <c r="H67" s="68" t="s">
@@ -4990,8 +5010,8 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="61"/>
+    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="52"/>
       <c r="B68" s="71">
         <v>34657</v>
       </c>
@@ -5017,8 +5037,8 @@
         <v>206</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="61"/>
+    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="52"/>
       <c r="B69" s="76">
         <v>34864</v>
       </c>
@@ -5044,8 +5064,8 @@
         <v>210</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="61"/>
+    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="52"/>
       <c r="B70" s="71">
         <v>34847</v>
       </c>
@@ -5071,12 +5091,12 @@
         <v>213</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="61"/>
+    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="52"/>
       <c r="B71" s="76">
         <v>34909</v>
       </c>
-      <c r="C71" s="81" t="s">
+      <c r="C71" s="80" t="s">
         <v>214</v>
       </c>
       <c r="D71" s="68" t="s">
@@ -5098,12 +5118,12 @@
         <v>217</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="61"/>
+    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="52"/>
       <c r="B72" s="71">
         <v>34910</v>
       </c>
-      <c r="C72" s="81" t="s">
+      <c r="C72" s="80" t="s">
         <v>218</v>
       </c>
       <c r="D72" s="73" t="s">
@@ -5125,186 +5145,186 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="61"/>
-      <c r="B73" s="82">
+    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="52"/>
+      <c r="B73" s="81">
         <v>35000</v>
       </c>
-      <c r="C73" s="83" t="s">
+      <c r="C73" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="D73" s="83" t="s">
+      <c r="D73" s="82" t="s">
         <v>223</v>
       </c>
-      <c r="E73" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="F73" s="83" t="s">
+      <c r="E73" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="F73" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="G73" s="84">
+      <c r="G73" s="83">
         <v>46047</v>
       </c>
-      <c r="H73" s="83" t="s">
+      <c r="H73" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="I73" s="85" t="s">
+      <c r="I73" s="84" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="61"/>
-      <c r="B74" s="61"/>
-      <c r="C74" s="61"/>
-      <c r="D74" s="61"/>
-      <c r="E74" s="61"/>
-      <c r="F74" s="61"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="61"/>
-      <c r="I74" s="61"/>
-    </row>
-    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="61"/>
-      <c r="B75" s="61"/>
-      <c r="C75" s="61"/>
-      <c r="D75" s="61"/>
-      <c r="E75" s="61"/>
-      <c r="F75" s="61"/>
-      <c r="G75" s="61"/>
-      <c r="H75" s="61"/>
-      <c r="I75" s="61"/>
-    </row>
-    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="61"/>
-      <c r="B76" s="61"/>
-      <c r="C76" s="61"/>
-      <c r="D76" s="61"/>
-      <c r="E76" s="61"/>
-      <c r="F76" s="61"/>
-      <c r="G76" s="61"/>
-      <c r="H76" s="61"/>
-      <c r="I76" s="61"/>
-    </row>
-    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="61"/>
-      <c r="B77" s="61"/>
-      <c r="C77" s="61"/>
-      <c r="D77" s="61"/>
-      <c r="E77" s="61"/>
-      <c r="F77" s="61"/>
-      <c r="G77" s="61"/>
-      <c r="H77" s="61"/>
-      <c r="I77" s="61"/>
-    </row>
-    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="61"/>
-      <c r="B78" s="61"/>
-      <c r="C78" s="61"/>
-      <c r="D78" s="61"/>
-      <c r="E78" s="61"/>
-      <c r="F78" s="61"/>
-      <c r="G78" s="61"/>
-      <c r="H78" s="61"/>
-      <c r="I78" s="61"/>
-    </row>
-    <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="61"/>
-      <c r="B79" s="61"/>
-      <c r="C79" s="61"/>
-      <c r="D79" s="61"/>
-      <c r="E79" s="61"/>
-      <c r="F79" s="61"/>
-      <c r="G79" s="61"/>
-      <c r="H79" s="61"/>
-      <c r="I79" s="61"/>
-    </row>
-    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="61"/>
-      <c r="B80" s="86" t="s">
+    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="52"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="52"/>
+      <c r="G74" s="52"/>
+      <c r="H74" s="52"/>
+      <c r="I74" s="52"/>
+    </row>
+    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
+    </row>
+    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
+    </row>
+    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="52"/>
+      <c r="B77" s="52"/>
+      <c r="C77" s="52"/>
+      <c r="D77" s="52"/>
+      <c r="E77" s="52"/>
+      <c r="F77" s="52"/>
+      <c r="G77" s="52"/>
+      <c r="H77" s="52"/>
+      <c r="I77" s="52"/>
+    </row>
+    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="52"/>
+      <c r="B78" s="52"/>
+      <c r="C78" s="52"/>
+      <c r="D78" s="52"/>
+      <c r="E78" s="52"/>
+      <c r="F78" s="52"/>
+      <c r="G78" s="52"/>
+      <c r="H78" s="52"/>
+      <c r="I78" s="52"/>
+    </row>
+    <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="52"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
+      <c r="I79" s="52"/>
+    </row>
+    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="52"/>
+      <c r="B80" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="87"/>
-      <c r="D80" s="61"/>
-      <c r="E80" s="61"/>
-      <c r="F80" s="61"/>
-      <c r="G80" s="61"/>
-      <c r="H80" s="61"/>
-      <c r="I80" s="61"/>
-    </row>
-    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="61"/>
-      <c r="B81" s="88" t="s">
+      <c r="C80" s="100"/>
+      <c r="D80" s="52"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="52"/>
+      <c r="G80" s="52"/>
+      <c r="H80" s="52"/>
+      <c r="I80" s="52"/>
+    </row>
+    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="52"/>
+      <c r="B81" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="C81" s="89" t="s">
+      <c r="C81" s="59" t="s">
         <v>225</v>
       </c>
-      <c r="D81" s="61"/>
-      <c r="E81" s="61"/>
-      <c r="F81" s="61"/>
-      <c r="G81" s="61"/>
-      <c r="H81" s="61"/>
-      <c r="I81" s="61"/>
-    </row>
-    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="61"/>
-      <c r="B82" s="90" t="s">
+      <c r="D81" s="52"/>
+      <c r="E81" s="52"/>
+      <c r="F81" s="52"/>
+      <c r="G81" s="52"/>
+      <c r="H81" s="52"/>
+      <c r="I81" s="52"/>
+    </row>
+    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="52"/>
+      <c r="B82" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C82" s="91" t="s">
+      <c r="C82" s="61" t="s">
         <v>226</v>
       </c>
-      <c r="D82" s="61"/>
-      <c r="E82" s="61"/>
-      <c r="F82" s="61"/>
-      <c r="G82" s="61"/>
-      <c r="H82" s="61"/>
-      <c r="I82" s="61"/>
-    </row>
-    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="61"/>
-      <c r="B83" s="88" t="s">
+      <c r="D82" s="52"/>
+      <c r="E82" s="52"/>
+      <c r="F82" s="52"/>
+      <c r="G82" s="52"/>
+      <c r="H82" s="52"/>
+      <c r="I82" s="52"/>
+    </row>
+    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="52"/>
+      <c r="B83" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="C83" s="89" t="s">
+      <c r="C83" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="D83" s="61"/>
-      <c r="E83" s="61"/>
-      <c r="F83" s="61"/>
-      <c r="G83" s="61"/>
-      <c r="H83" s="61"/>
-      <c r="I83" s="61"/>
-    </row>
-    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="61"/>
-      <c r="B84" s="90" t="s">
+      <c r="D83" s="52"/>
+      <c r="E83" s="52"/>
+      <c r="F83" s="52"/>
+      <c r="G83" s="52"/>
+      <c r="H83" s="52"/>
+      <c r="I83" s="52"/>
+    </row>
+    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="52"/>
+      <c r="B84" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="C84" s="91" t="s">
+      <c r="C84" s="61" t="s">
         <v>228</v>
       </c>
-      <c r="D84" s="61"/>
-      <c r="E84" s="61"/>
-      <c r="F84" s="61"/>
-      <c r="G84" s="61"/>
-      <c r="H84" s="61"/>
-      <c r="I84" s="61"/>
-    </row>
-    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="61"/>
-      <c r="B85" s="92" t="s">
+      <c r="D84" s="52"/>
+      <c r="E84" s="52"/>
+      <c r="F84" s="52"/>
+      <c r="G84" s="52"/>
+      <c r="H84" s="52"/>
+      <c r="I84" s="52"/>
+    </row>
+    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="52"/>
+      <c r="B85" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="C85" s="93" t="s">
+      <c r="C85" s="63" t="s">
         <v>229</v>
       </c>
-      <c r="D85" s="61"/>
-      <c r="E85" s="61"/>
-      <c r="F85" s="61"/>
-      <c r="G85" s="61"/>
-      <c r="H85" s="61"/>
-      <c r="I85" s="61"/>
+      <c r="D85" s="52"/>
+      <c r="E85" s="52"/>
+      <c r="F85" s="52"/>
+      <c r="G85" s="52"/>
+      <c r="H85" s="52"/>
+      <c r="I85" s="52"/>
     </row>
   </sheetData>
   <autoFilter ref="H1:H85" xr:uid="{C0AF269B-23FC-48D2-A16F-AEFC2A32B111}"/>
@@ -5679,7 +5699,7 @@
       <c r="B20" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="88" t="s">
         <v>188</v>
       </c>
       <c r="D20" s="41" t="s">
@@ -6421,29 +6441,265 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="55">
-        <v>35092</v>
+      <c r="A64" s="109">
+        <v>35169</v>
       </c>
       <c r="B64" t="s">
-        <v>355</v>
-      </c>
-      <c r="C64" s="56" t="s">
-        <v>356</v>
+        <v>361</v>
+      </c>
+      <c r="C64" s="111" t="s">
+        <v>360</v>
       </c>
       <c r="D64" s="41" t="s">
         <v>44</v>
+      </c>
+      <c r="E64" s="110">
+        <v>581517848</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C20" r:id="rId1" xr:uid="{E9067DAE-307E-4DE5-9C07-6483F3D90ADA}"/>
-    <hyperlink ref="C64" r:id="rId2" xr:uid="{15B98ED2-9FBE-4C47-B8BF-B3BD25E93FF5}"/>
+    <hyperlink ref="C64" r:id="rId2" xr:uid="{4D6DBEFF-03F0-4584-8268-523AD0EEBC39}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2936E37-DEB4-44C1-8A8C-AE4DEA8D7043}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="102" t="s">
+        <v>359</v>
+      </c>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="104"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="92">
+        <v>28409</v>
+      </c>
+      <c r="B2" s="89" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2" s="90" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="89" t="s">
+        <v>357</v>
+      </c>
+      <c r="E2" s="93">
+        <v>546380314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="92">
+        <v>28941</v>
+      </c>
+      <c r="B3" s="89" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" s="90" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="89" t="s">
+        <v>358</v>
+      </c>
+      <c r="E3" s="93">
+        <v>532022999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="92">
+        <v>29741</v>
+      </c>
+      <c r="B4" s="89" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" s="90" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="89" t="s">
+        <v>358</v>
+      </c>
+      <c r="E4" s="93">
+        <v>558183173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="94">
+        <v>32427</v>
+      </c>
+      <c r="B5" s="89" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="90" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="93">
+        <v>582259125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="92">
+        <v>34168</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="90" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="93">
+        <v>503544881</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="92">
+        <v>31956</v>
+      </c>
+      <c r="B7" s="89" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="90" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="93">
+        <v>598948116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="92">
+        <v>34500</v>
+      </c>
+      <c r="B8" s="91" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="93">
+        <v>531415743</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="92">
+        <v>33579</v>
+      </c>
+      <c r="B9" s="89" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="90" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="93">
+        <v>508555012</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="92">
+        <v>31955</v>
+      </c>
+      <c r="B10" s="89" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" s="90" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="93">
+        <v>551148108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="92">
+        <v>33094</v>
+      </c>
+      <c r="B11" s="89" t="s">
+        <v>296</v>
+      </c>
+      <c r="C11" s="90" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="93">
+        <v>580184755</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="92">
+        <v>34689</v>
+      </c>
+      <c r="B12" s="91" t="s">
+        <v>301</v>
+      </c>
+      <c r="C12" s="90" t="s">
+        <v>202</v>
+      </c>
+      <c r="D12" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="93">
+        <v>535672392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="95">
+        <v>35000</v>
+      </c>
+      <c r="B13" s="96" t="s">
+        <v>355</v>
+      </c>
+      <c r="C13" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="98" t="s">
+        <v>356</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{887A3C45-2914-4BEF-A085-E8DA9CF84D43}">
   <dimension ref="A3:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6552,7 +6808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A300AFEA-8914-478B-B995-C110AA1208AE}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6578,18 +6834,18 @@
       <c r="C1" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="57" t="s">
+      <c r="D1" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="E1" s="58"/>
+      <c r="E1" s="106"/>
       <c r="F1" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="107" t="s">
         <v>320</v>
       </c>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -6601,10 +6857,10 @@
       <c r="C2" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="108" t="s">
         <v>324</v>
       </c>
-      <c r="E2" s="60"/>
+      <c r="E2" s="108"/>
       <c r="F2" s="11" t="s">
         <v>325</v>
       </c>
@@ -6684,7 +6940,7 @@
       <c r="G5" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="86" t="s">
         <v>341</v>
       </c>
       <c r="I5" s="21"/>
@@ -6704,7 +6960,7 @@
       <c r="F6" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="86" t="s">
         <v>344</v>
       </c>
       <c r="H6" s="21" t="s">
@@ -6768,7 +7024,7 @@
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="53"/>
+      <c r="B13" s="87"/>
       <c r="C13" t="s">
         <v>349</v>
       </c>
@@ -6814,7 +7070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7325098A-1B83-4F7B-8AF7-9D6AF9F81E18}">
   <dimension ref="A2:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6882,15 +7138,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010057D8301AF2E034448D383AD6059623AD" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="010fb9c2226637447a522e2c91231dad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3491a11-7bba-4833-9e13-347a8af23878" xmlns:ns3="60327604-53ae-4893-9616-7899fcf99eb8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9c222462a19b0f1a46af5cffa3dc3b93" ns2:_="" ns3:_="">
     <xsd:import namespace="c3491a11-7bba-4833-9e13-347a8af23878"/>
@@ -7150,7 +7397,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
@@ -7166,15 +7413,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD1400B-BCE6-4CA2-9823-1B96B380417C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7193,7 +7441,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7202,4 +7450,12 @@
     <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/IDI_Team.xlsx
+++ b/IDI_Team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\rd6_generator_tool\rd6_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652225D0-F53F-4F2D-9D8A-14179060BE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DC7F75-A9F4-498E-9A31-20C3077E3772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5ABAA1C1-B119-44A8-8322-349E275CC8CB}"/>
   </bookViews>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="362">
   <si>
     <t>KSA STAFF</t>
   </si>
@@ -1910,6 +1910,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1936,9 +1939,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -2826,7 +2826,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7165A24-A7E6-4B06-A81F-C5410B69138D}" name="Tableau croisé dynamique1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7165A24-A7E6-4B06-A81F-C5410B69138D}" name="Tableau croisé dynamique1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:E10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -3261,11 +3261,11 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="52"/>
       <c r="B2" s="52"/>
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
       <c r="F2" s="52"/>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -5240,10 +5240,10 @@
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="52"/>
-      <c r="B80" s="99" t="s">
+      <c r="B80" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="100"/>
+      <c r="C80" s="103"/>
       <c r="D80" s="52"/>
       <c r="E80" s="52"/>
       <c r="F80" s="52"/>
@@ -6441,19 +6441,19 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="109">
+      <c r="A64" s="99">
         <v>35169</v>
       </c>
       <c r="B64" t="s">
         <v>361</v>
       </c>
-      <c r="C64" s="111" t="s">
+      <c r="C64" s="101" t="s">
         <v>360</v>
       </c>
       <c r="D64" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="110">
+      <c r="E64" s="100">
         <v>581517848</v>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2936E37-DEB4-44C1-8A8C-AE4DEA8D7043}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -6479,13 +6479,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="105" t="s">
         <v>359</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="104"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="92">
@@ -6689,12 +6689,32 @@
       </c>
       <c r="E13" s="98" t="s">
         <v>356</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="99">
+        <v>35169</v>
+      </c>
+      <c r="B14" t="s">
+        <v>361</v>
+      </c>
+      <c r="C14" s="101" t="s">
+        <v>360</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="100">
+        <v>581517848</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C14" r:id="rId1" xr:uid="{F02ECD66-7434-4C48-8F0A-C4E2C1972DEF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6834,18 +6854,18 @@
       <c r="C1" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="105" t="s">
+      <c r="D1" s="108" t="s">
         <v>318</v>
       </c>
-      <c r="E1" s="106"/>
+      <c r="E1" s="109"/>
       <c r="F1" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="G1" s="107" t="s">
+      <c r="G1" s="110" t="s">
         <v>320</v>
       </c>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -6857,10 +6877,10 @@
       <c r="C2" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="111" t="s">
         <v>324</v>
       </c>
-      <c r="E2" s="108"/>
+      <c r="E2" s="111"/>
       <c r="F2" s="11" t="s">
         <v>325</v>
       </c>
@@ -7138,6 +7158,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
+    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </hyperlink>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010057D8301AF2E034448D383AD6059623AD" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="010fb9c2226637447a522e2c91231dad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3491a11-7bba-4833-9e13-347a8af23878" xmlns:ns3="60327604-53ae-4893-9616-7899fcf99eb8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9c222462a19b0f1a46af5cffa3dc3b93" ns2:_="" ns3:_="">
     <xsd:import namespace="c3491a11-7bba-4833-9e13-347a8af23878"/>
@@ -7397,32 +7442,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
-    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </hyperlink>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
+    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD1400B-BCE6-4CA2-9823-1B96B380417C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7439,23 +7478,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
-    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/IDI_Team.xlsx
+++ b/IDI_Team.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\rd6_generator_tool\rd6_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DC7F75-A9F4-498E-9A31-20C3077E3772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1AA643-C082-4012-AB02-77E30BF7464C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5ABAA1C1-B119-44A8-8322-349E275CC8CB}"/>
   </bookViews>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="362">
   <si>
     <t>KSA STAFF</t>
   </si>
@@ -1672,7 +1672,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1938,6 +1938,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2826,7 +2829,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7165A24-A7E6-4B06-A81F-C5410B69138D}" name="Tableau croisé dynamique1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7165A24-A7E6-4B06-A81F-C5410B69138D}" name="Tableau croisé dynamique1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:E10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -5359,7 +5362,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD185231-ACFC-4ED8-BF5C-5C285BF0ABA2}">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -6457,10 +6460,28 @@
         <v>581517848</v>
       </c>
     </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="38">
+        <v>35000</v>
+      </c>
+      <c r="B65" s="39" t="s">
+        <v>355</v>
+      </c>
+      <c r="C65" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="D65" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E65" s="112" t="s">
+        <v>356</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C20" r:id="rId1" xr:uid="{E9067DAE-307E-4DE5-9C07-6483F3D90ADA}"/>
     <hyperlink ref="C64" r:id="rId2" xr:uid="{4D6DBEFF-03F0-4584-8268-523AD0EEBC39}"/>
+    <hyperlink ref="C65" r:id="rId3" xr:uid="{3E79D7DA-725B-4095-B5D0-BCC4BC67B0FA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7167,22 +7188,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
-    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </hyperlink>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010057D8301AF2E034448D383AD6059623AD" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="010fb9c2226637447a522e2c91231dad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3491a11-7bba-4833-9e13-347a8af23878" xmlns:ns3="60327604-53ae-4893-9616-7899fcf99eb8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9c222462a19b0f1a46af5cffa3dc3b93" ns2:_="" ns3:_="">
     <xsd:import namespace="c3491a11-7bba-4833-9e13-347a8af23878"/>
@@ -7442,6 +7447,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
+    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </hyperlink>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
   <ds:schemaRefs>
@@ -7451,17 +7472,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
-    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD1400B-BCE6-4CA2-9823-1B96B380417C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7478,4 +7488,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
+    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/IDI_Team.xlsx
+++ b/IDI_Team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\rd6_generator_tool\rd6_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1AA643-C082-4012-AB02-77E30BF7464C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BC4A9A-6C92-44E5-86A6-1CF5F8DD0DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5ABAA1C1-B119-44A8-8322-349E275CC8CB}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="365">
   <si>
     <t>KSA STAFF</t>
   </si>
@@ -1136,6 +1136,15 @@
   </si>
   <si>
     <t>Ayman ASHRAF</t>
+  </si>
+  <si>
+    <t>Raneem ALHARBI</t>
+  </si>
+  <si>
+    <t>raneem.alharbi@socotec.com</t>
+  </si>
+  <si>
+    <t>Civil Eng / Coordinator</t>
   </si>
 </sst>
 </file>
@@ -1672,7 +1681,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1913,6 +1922,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1939,9 +1951,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -3264,11 +3277,11 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="52"/>
       <c r="B2" s="52"/>
-      <c r="C2" s="104" t="s">
+      <c r="C2" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
       <c r="F2" s="52"/>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -5243,10 +5256,10 @@
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="52"/>
-      <c r="B80" s="102" t="s">
+      <c r="B80" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="103"/>
+      <c r="C80" s="104"/>
       <c r="D80" s="52"/>
       <c r="E80" s="52"/>
       <c r="F80" s="52"/>
@@ -5362,7 +5375,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD185231-ACFC-4ED8-BF5C-5C285BF0ABA2}">
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -6473,8 +6486,25 @@
       <c r="D65" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="E65" s="112" t="s">
+      <c r="E65" s="102" t="s">
         <v>356</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="114">
+        <v>35350</v>
+      </c>
+      <c r="B66" s="113" t="s">
+        <v>362</v>
+      </c>
+      <c r="C66" s="115" t="s">
+        <v>363</v>
+      </c>
+      <c r="D66" s="41" t="s">
+        <v>364</v>
+      </c>
+      <c r="E66" s="116">
+        <v>573842426</v>
       </c>
     </row>
   </sheetData>
@@ -6482,6 +6512,7 @@
     <hyperlink ref="C20" r:id="rId1" xr:uid="{E9067DAE-307E-4DE5-9C07-6483F3D90ADA}"/>
     <hyperlink ref="C64" r:id="rId2" xr:uid="{4D6DBEFF-03F0-4584-8268-523AD0EEBC39}"/>
     <hyperlink ref="C65" r:id="rId3" xr:uid="{3E79D7DA-725B-4095-B5D0-BCC4BC67B0FA}"/>
+    <hyperlink ref="C66" r:id="rId4" xr:uid="{0BEE51F5-C72E-4891-AA34-9D1F55F05212}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6500,13 +6531,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="106" t="s">
         <v>359</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="92">
@@ -6875,18 +6906,18 @@
       <c r="C1" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="108" t="s">
+      <c r="D1" s="109" t="s">
         <v>318</v>
       </c>
-      <c r="E1" s="109"/>
+      <c r="E1" s="110"/>
       <c r="F1" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="G1" s="110" t="s">
+      <c r="G1" s="111" t="s">
         <v>320</v>
       </c>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -6898,10 +6929,10 @@
       <c r="C2" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="D2" s="111" t="s">
+      <c r="D2" s="112" t="s">
         <v>324</v>
       </c>
-      <c r="E2" s="111"/>
+      <c r="E2" s="112"/>
       <c r="F2" s="11" t="s">
         <v>325</v>
       </c>
@@ -7188,6 +7219,22 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
+    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </hyperlink>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010057D8301AF2E034448D383AD6059623AD" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="010fb9c2226637447a522e2c91231dad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3491a11-7bba-4833-9e13-347a8af23878" xmlns:ns3="60327604-53ae-4893-9616-7899fcf99eb8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9c222462a19b0f1a46af5cffa3dc3b93" ns2:_="" ns3:_="">
     <xsd:import namespace="c3491a11-7bba-4833-9e13-347a8af23878"/>
@@ -7447,22 +7494,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
-    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </hyperlink>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
   <ds:schemaRefs>
@@ -7472,6 +7503,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
+    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD1400B-BCE6-4CA2-9823-1B96B380417C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7488,15 +7530,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
-    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/IDI_Team.xlsx
+++ b/IDI_Team.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\rd6_generator_tool\rd6_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BC4A9A-6C92-44E5-86A6-1CF5F8DD0DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A69253A-B39C-46E1-902C-9243E8367F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5ABAA1C1-B119-44A8-8322-349E275CC8CB}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="367">
   <si>
     <t>KSA STAFF</t>
   </si>
@@ -1145,6 +1145,12 @@
   </si>
   <si>
     <t>Civil Eng / Coordinator</t>
+  </si>
+  <si>
+    <t>Sultan HEJAZI</t>
+  </si>
+  <si>
+    <t>sultan.hejazi@socotec.com</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1687,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1925,6 +1931,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1951,9 +1959,8 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -3277,11 +3284,11 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="52"/>
       <c r="B2" s="52"/>
-      <c r="C2" s="105" t="s">
+      <c r="C2" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
       <c r="F2" s="52"/>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -5256,10 +5263,10 @@
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="52"/>
-      <c r="B80" s="103" t="s">
+      <c r="B80" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="104"/>
+      <c r="C80" s="106"/>
       <c r="D80" s="52"/>
       <c r="E80" s="52"/>
       <c r="F80" s="52"/>
@@ -5375,7 +5382,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD185231-ACFC-4ED8-BF5C-5C285BF0ABA2}">
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -6491,20 +6498,37 @@
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="114">
+      <c r="A66" s="99">
         <v>35350</v>
       </c>
-      <c r="B66" s="113" t="s">
+      <c r="B66" s="103" t="s">
         <v>362</v>
       </c>
-      <c r="C66" s="115" t="s">
+      <c r="C66" s="104" t="s">
         <v>363</v>
       </c>
       <c r="D66" s="41" t="s">
         <v>364</v>
       </c>
-      <c r="E66" s="116">
+      <c r="E66" s="100">
         <v>573842426</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="115">
+        <v>35692</v>
+      </c>
+      <c r="B67" s="116" t="s">
+        <v>365</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D67" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E67" s="117">
+        <v>561508684</v>
       </c>
     </row>
   </sheetData>
@@ -6513,6 +6537,7 @@
     <hyperlink ref="C64" r:id="rId2" xr:uid="{4D6DBEFF-03F0-4584-8268-523AD0EEBC39}"/>
     <hyperlink ref="C65" r:id="rId3" xr:uid="{3E79D7DA-725B-4095-B5D0-BCC4BC67B0FA}"/>
     <hyperlink ref="C66" r:id="rId4" xr:uid="{0BEE51F5-C72E-4891-AA34-9D1F55F05212}"/>
+    <hyperlink ref="C67" r:id="rId5" xr:uid="{FBDC3DBF-B36B-44F8-A83E-B4F5A3DEB4B9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6531,13 +6556,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="108" t="s">
         <v>359</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="108"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="110"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="92">
@@ -6906,18 +6931,18 @@
       <c r="C1" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="111" t="s">
         <v>318</v>
       </c>
-      <c r="E1" s="110"/>
+      <c r="E1" s="112"/>
       <c r="F1" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="G1" s="111" t="s">
+      <c r="G1" s="113" t="s">
         <v>320</v>
       </c>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -6929,10 +6954,10 @@
       <c r="C2" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="D2" s="112" t="s">
+      <c r="D2" s="114" t="s">
         <v>324</v>
       </c>
-      <c r="E2" s="112"/>
+      <c r="E2" s="114"/>
       <c r="F2" s="11" t="s">
         <v>325</v>
       </c>
@@ -7210,31 +7235,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
-    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </hyperlink>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010057D8301AF2E034448D383AD6059623AD" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="010fb9c2226637447a522e2c91231dad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3491a11-7bba-4833-9e13-347a8af23878" xmlns:ns3="60327604-53ae-4893-9616-7899fcf99eb8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9c222462a19b0f1a46af5cffa3dc3b93" ns2:_="" ns3:_="">
     <xsd:import namespace="c3491a11-7bba-4833-9e13-347a8af23878"/>
@@ -7494,10 +7494,46 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
+    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </hyperlink>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD1400B-BCE6-4CA2-9823-1B96B380417C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
+    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7514,20 +7550,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD1400B-BCE6-4CA2-9823-1B96B380417C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
-    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/IDI_Team.xlsx
+++ b/IDI_Team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\rd6_generator_tool\rd6_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A69253A-B39C-46E1-902C-9243E8367F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B824C3-B726-478B-ACBA-44373D39EDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5ABAA1C1-B119-44A8-8322-349E275CC8CB}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="368">
   <si>
     <t>KSA STAFF</t>
   </si>
@@ -1151,6 +1151,9 @@
   </si>
   <si>
     <t>sultan.hejazi@socotec.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YOUSEF Younis </t>
   </si>
 </sst>
 </file>
@@ -1687,7 +1690,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1959,9 +1962,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -6434,7 +6434,7 @@
         <v>34689</v>
       </c>
       <c r="B62" s="39" t="s">
-        <v>301</v>
+        <v>367</v>
       </c>
       <c r="C62" s="40" t="s">
         <v>202</v>
@@ -6515,10 +6515,10 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="115">
+      <c r="A67" s="99">
         <v>35692</v>
       </c>
-      <c r="B67" s="116" t="s">
+      <c r="B67" s="103" t="s">
         <v>365</v>
       </c>
       <c r="C67" s="2" t="s">
@@ -6527,7 +6527,7 @@
       <c r="D67" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="E67" s="117">
+      <c r="E67" s="100">
         <v>561508684</v>
       </c>
     </row>
@@ -7235,6 +7235,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
+    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </hyperlink>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010057D8301AF2E034448D383AD6059623AD" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="010fb9c2226637447a522e2c91231dad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3491a11-7bba-4833-9e13-347a8af23878" xmlns:ns3="60327604-53ae-4893-9616-7899fcf99eb8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9c222462a19b0f1a46af5cffa3dc3b93" ns2:_="" ns3:_="">
     <xsd:import namespace="c3491a11-7bba-4833-9e13-347a8af23878"/>
@@ -7494,32 +7519,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="60327604-53ae-4893-9616-7899fcf99eb8" xsi:nil="true"/>
-    <hyperlink xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </hyperlink>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3491a11-7bba-4833-9e13-347a8af23878">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="c3491a11-7bba-4833-9e13-347a8af23878" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
+    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FD1400B-BCE6-4CA2-9823-1B96B380417C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7536,23 +7555,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2507D038-748D-4DCE-A6AB-F5AD243863A6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="60327604-53ae-4893-9616-7899fcf99eb8"/>
-    <ds:schemaRef ds:uri="c3491a11-7bba-4833-9e13-347a8af23878"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4881033E-FD87-4678-BCAF-4F75596F2B0B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>